--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E073E12-B388-4F0A-9ED6-765626949A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527CAF80-232E-4D61-9C88-2423627D0C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="6210" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>No</t>
   </si>
@@ -68,6 +68,21 @@
   </si>
   <si>
     <t>Date of Birth (year-month-date)</t>
+  </si>
+  <si>
+    <t>Terms:</t>
+  </si>
+  <si>
+    <t>1. Please fill in the table on the left with all the participants who attended.</t>
+  </si>
+  <si>
+    <t>2. Please do not change the table structure.</t>
+  </si>
+  <si>
+    <t>3. Please follow the example format for filling it out.</t>
+  </si>
+  <si>
+    <t>4. Please save the file after completion and upload it back to the registration page.</t>
   </si>
 </sst>
 </file>
@@ -75,7 +90,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -129,13 +144,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -354,36 +378,36 @@
   <dimension ref="A1:I1000"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
-    <col min="3" max="3" width="16.75" customWidth="1"/>
-    <col min="4" max="4" width="13.375" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="22.125" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="30.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -397,7 +421,7 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="6">
         <v>80989999</v>
       </c>
       <c r="E2" s="3">
@@ -436,11 +460,31 @@
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
